--- a/imports/hackathon-import-template.xlsx
+++ b/imports/hackathon-import-template.xlsx
@@ -546,7 +546,7 @@
         <v>فريق المياه</v>
       </c>
       <c r="B2" t="str">
-        <v>إثراء تجربة ضيوف الرحمن في المدن المقدسة</v>
+        <v>المسار التقني</v>
       </c>
       <c r="C2" t="str">
         <v>حل ذكي لرصد تسربات شبكات المياه</v>
@@ -588,6 +588,9 @@
     <row r="3">
       <c r="A3" t="str">
         <v>فريق الاستدامة</v>
+      </c>
+      <c r="B3" t="str">
+        <v>المسار التقني</v>
       </c>
       <c r="C3" t="str">
         <v>منصة لترشيد الاستهلاك المنزلي</v>
@@ -662,7 +665,7 @@
         <v>فريق المياه</v>
       </c>
       <c r="B2" t="str">
-        <v>إثراء تجربة ضيوف الرحمن في المدن المقدسة</v>
+        <v>المسار التقني</v>
       </c>
       <c r="C2" t="str">
         <v>حل ذكي لرصد تسربات شبكات المياه</v>
@@ -1529,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A15"/>
   <cols>
     <col min="1" max="1" width="46.83203125" customWidth="1"/>
   </cols>
@@ -1541,72 +1544,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>تعزيز الدمج المجتمعي لكبار السن والمكفوفين</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>إثراء تجربة ضيوف الرحمن في المدن المقدسة</v>
+        <v>المسار التقني</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>الحلول الاجتماعية المستدامة</v>
+        <v>المجال المهني (professionalField)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ذكاء اصناعي</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>المجال المهني (professionalField)</v>
+        <v>علم البيانات</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ذكاء اصناعي</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>علم البيانات</v>
+        <v>برمجة</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>برمجة</v>
+        <v>الجنس (gender)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ذكر</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>الجنس (gender)</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>ذكر</v>
+        <v>أنثى</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>أنثى</v>
+        <v>القيم المنطقية</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TRUE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>القيم المنطقية</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>TRUE</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
         <v>FALSE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/imports/hackathon-import-template.xlsx
+++ b/imports/hackathon-import-template.xlsx
@@ -576,7 +576,7 @@
         <v>علوم حاسب</v>
       </c>
       <c r="L2" t="str">
-        <v>برمجة</v>
+        <v>التقنية</v>
       </c>
       <c r="M2" t="str">
         <v>https://github.com/sara</v>
@@ -620,7 +620,7 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>علم البيانات</v>
+        <v>التصميم</v>
       </c>
       <c r="M3" t="str">
         <v>https://github.com/omar</v>
@@ -760,7 +760,7 @@
         <v>علوم حاسب</v>
       </c>
       <c r="H2" t="str">
-        <v>برمجة</v>
+        <v>التقنية</v>
       </c>
       <c r="I2" t="str">
         <v>https://github.com/sara</v>
@@ -798,7 +798,7 @@
         <v>هندسة</v>
       </c>
       <c r="H3" t="str">
-        <v>علم البيانات</v>
+        <v>التصميم</v>
       </c>
       <c r="I3" t="str">
         <v>https://github.com/omar</v>
@@ -836,7 +836,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>ذكاء اصناعي</v>
+        <v>التنفيذ والأثر</v>
       </c>
       <c r="I4" t="str">
         <v>https://github.com/huda</v>
@@ -1146,7 +1146,7 @@
         <v>اختياري</v>
       </c>
       <c r="E13" t="str">
-        <v>ذكاء اصناعي | علم البيانات | برمجة</v>
+        <v>الطفولة والمجالات المهنية | التقنية | التصميم | التنفيذ والأثر</v>
       </c>
     </row>
     <row r="14">
@@ -1316,7 +1316,7 @@
         <v>اختياري</v>
       </c>
       <c r="E23" t="str">
-        <v>ذكاء اصناعي | علم البيانات | برمجة</v>
+        <v>الطفولة والمجالات المهنية | التقنية | التصميم | التنفيذ والأثر</v>
       </c>
     </row>
     <row r="24">
@@ -1532,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <cols>
     <col min="1" max="1" width="46.83203125" customWidth="1"/>
   </cols>
@@ -1554,52 +1554,57 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ذكاء اصناعي</v>
+        <v>الطفولة والمجالات المهنية</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>علم البيانات</v>
+        <v>التقنية</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>برمجة</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>الجنس (gender)</v>
+        <v>التصميم</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>التنفيذ والأثر</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ذكر</v>
+        <v>الجنس (gender)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>ذكر</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>أنثى</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>القيم المنطقية</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TRUE</v>
+        <v>القيم المنطقية</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>FALSE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A16"/>
   </ignoredErrors>
 </worksheet>
 </file>